--- a/basis_set/val/Pruned_V_GMM_ca_cb_15x15tables.xlsx
+++ b/basis_set/val/Pruned_V_GMM_ca_cb_15x15tables.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F97"/>
+  <dimension ref="A1:F102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -947,1628 +947,1738 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>C10</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>219</v>
+        <v>31</v>
       </c>
       <c r="C24" t="n">
-        <v>60.28558303860446</v>
+        <v>62.20475381178428</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4200061725872154</v>
+        <v>0.2821288596759247</v>
       </c>
       <c r="E24" t="n">
-        <v>32.76941552511416</v>
+        <v>31.04480645161289</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5416887182889522</v>
+        <v>0.2814456825329555</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>D03</t>
+          <t>D02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1094</v>
+        <v>219</v>
       </c>
       <c r="C25" t="n">
-        <v>62.0746651644903</v>
+        <v>60.28558303860446</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3532646469799793</v>
+        <v>0.4200061725872154</v>
       </c>
       <c r="E25" t="n">
-        <v>33.85560968921389</v>
+        <v>32.76941552511416</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3668172815468247</v>
+        <v>0.5416887182889522</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>D04</t>
+          <t>D03</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5264</v>
+        <v>1094</v>
       </c>
       <c r="C26" t="n">
-        <v>61.61027279877494</v>
+        <v>62.0746651644903</v>
       </c>
       <c r="D26" t="n">
-        <v>0.341013593463136</v>
+        <v>0.3532646469799793</v>
       </c>
       <c r="E26" t="n">
-        <v>33.53310122126485</v>
+        <v>33.85560968921389</v>
       </c>
       <c r="F26" t="n">
-        <v>0.413738552907548</v>
+        <v>0.3668172815468247</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>D05</t>
+          <t>D04</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5242</v>
+        <v>5264</v>
       </c>
       <c r="C27" t="n">
-        <v>61.65501215040195</v>
+        <v>61.61027279877494</v>
       </c>
       <c r="D27" t="n">
-        <v>0.351017988688549</v>
+        <v>0.341013593463136</v>
       </c>
       <c r="E27" t="n">
-        <v>32.65948760015264</v>
+        <v>33.53310122126485</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4611501061388114</v>
+        <v>0.413738552907548</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>D06</t>
+          <t>D05</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3914</v>
+        <v>5242</v>
       </c>
       <c r="C28" t="n">
-        <v>62.48719535865023</v>
+        <v>61.65501215040195</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4730032070176142</v>
+        <v>0.351017988688549</v>
       </c>
       <c r="E28" t="n">
-        <v>31.72761752682678</v>
+        <v>32.65948760015264</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4381778397211604</v>
+        <v>0.4611501061388114</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>D07</t>
+          <t>D06</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4958</v>
+        <v>3914</v>
       </c>
       <c r="C29" t="n">
-        <v>63.6934840661557</v>
+        <v>62.48719535865023</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5311563686781313</v>
+        <v>0.4730032070176142</v>
       </c>
       <c r="E29" t="n">
-        <v>31.29235921742638</v>
+        <v>31.72761752682678</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3688278220665131</v>
+        <v>0.4381778397211604</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>D08</t>
+          <t>D07</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3782</v>
+        <v>4958</v>
       </c>
       <c r="C30" t="n">
-        <v>64.66786829958583</v>
+        <v>63.6934840661557</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4056829855601507</v>
+        <v>0.5311563686781313</v>
       </c>
       <c r="E30" t="n">
-        <v>31.26267900581703</v>
+        <v>31.29235921742638</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3558482459849437</v>
+        <v>0.3688278220665131</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>D09</t>
+          <t>D08</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1636</v>
+        <v>3782</v>
       </c>
       <c r="C31" t="n">
-        <v>65.09404954906339</v>
+        <v>64.66786829958583</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3252824596662125</v>
+        <v>0.4056829855601507</v>
       </c>
       <c r="E31" t="n">
-        <v>31.15383068459657</v>
+        <v>31.26267900581703</v>
       </c>
       <c r="F31" t="n">
-        <v>0.3269123370263354</v>
+        <v>0.3558482459849437</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>D18</t>
+          <t>D09</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>109</v>
+        <v>1636</v>
       </c>
       <c r="C32" t="n">
-        <v>63.1458990825688</v>
+        <v>65.09404954906339</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3331470580580539</v>
+        <v>0.3252824596662125</v>
       </c>
       <c r="E32" t="n">
-        <v>22.80526605504588</v>
+        <v>31.15383068459657</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5536784935039839</v>
+        <v>0.3269123370263354</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>D18</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>38</v>
+        <v>109</v>
       </c>
       <c r="C33" t="n">
-        <v>61.24362162162203</v>
+        <v>63.1458990825688</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2685516560471469</v>
+        <v>0.3331470580580539</v>
       </c>
       <c r="E33" t="n">
-        <v>30.23694736842106</v>
+        <v>22.80526605504588</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2798002057266106</v>
+        <v>0.5536784935039839</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>598</v>
+        <v>38</v>
       </c>
       <c r="C34" t="n">
-        <v>61.98213635099987</v>
+        <v>61.24362162162203</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3609310162997258</v>
+        <v>0.2685516560471469</v>
       </c>
       <c r="E34" t="n">
-        <v>33.03519565217392</v>
+        <v>30.23694736842106</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3665876318434125</v>
+        <v>0.2798002057266106</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2303</v>
+        <v>598</v>
       </c>
       <c r="C35" t="n">
-        <v>61.50374641771602</v>
+        <v>61.98213635099987</v>
       </c>
       <c r="D35" t="n">
-        <v>0.4470155178166488</v>
+        <v>0.3609310162997258</v>
       </c>
       <c r="E35" t="n">
-        <v>32.61027138514979</v>
+        <v>33.03519565217392</v>
       </c>
       <c r="F35" t="n">
-        <v>0.4284597282927358</v>
+        <v>0.3665876318434125</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E04</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2787</v>
+        <v>2303</v>
       </c>
       <c r="C36" t="n">
-        <v>61.60774094007894</v>
+        <v>61.50374641771602</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3575484490513058</v>
+        <v>0.4470155178166488</v>
       </c>
       <c r="E36" t="n">
-        <v>31.6632436311446</v>
+        <v>32.61027138514979</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4179362415919961</v>
+        <v>0.4284597282927358</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>E06</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2722</v>
+        <v>2787</v>
       </c>
       <c r="C37" t="n">
-        <v>62.29538133725202</v>
+        <v>61.60774094007894</v>
       </c>
       <c r="D37" t="n">
-        <v>0.4396834870252118</v>
+        <v>0.3575484490513058</v>
       </c>
       <c r="E37" t="n">
-        <v>30.84464915503306</v>
+        <v>31.6632436311446</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4336764386834511</v>
+        <v>0.4179362415919961</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>E07</t>
+          <t>E06</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2618</v>
+        <v>2722</v>
       </c>
       <c r="C38" t="n">
-        <v>63.39731932773108</v>
+        <v>62.29538133725202</v>
       </c>
       <c r="D38" t="n">
-        <v>0.4352291139216774</v>
+        <v>0.4396834870252118</v>
       </c>
       <c r="E38" t="n">
-        <v>30.46068067226891</v>
+        <v>30.84464915503306</v>
       </c>
       <c r="F38" t="n">
-        <v>0.3742597506794125</v>
+        <v>0.4336764386834511</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>E08</t>
+          <t>E07</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>681</v>
+        <v>2618</v>
       </c>
       <c r="C39" t="n">
-        <v>64.37581204111601</v>
+        <v>63.39731932773108</v>
       </c>
       <c r="D39" t="n">
-        <v>0.4042892113742</v>
+        <v>0.4352291139216774</v>
       </c>
       <c r="E39" t="n">
-        <v>30.36022173274596</v>
+        <v>30.46068067226891</v>
       </c>
       <c r="F39" t="n">
-        <v>0.3538067005836774</v>
+        <v>0.3742597506794125</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>F04</t>
+          <t>E08</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>423</v>
+        <v>681</v>
       </c>
       <c r="C40" t="n">
-        <v>61.29966113744076</v>
+        <v>64.37581204111601</v>
       </c>
       <c r="D40" t="n">
-        <v>0.3794213121209681</v>
+        <v>0.4042892113742</v>
       </c>
       <c r="E40" t="n">
-        <v>31.96452606635071</v>
+        <v>30.36022173274596</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3561542519980352</v>
+        <v>0.3538067005836774</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>F05</t>
+          <t>E09</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>794</v>
+        <v>65</v>
       </c>
       <c r="C41" t="n">
-        <v>61.30986397984888</v>
+        <v>64.84901612903226</v>
       </c>
       <c r="D41" t="n">
-        <v>0.4493098336189401</v>
+        <v>0.3010133686847666</v>
       </c>
       <c r="E41" t="n">
-        <v>30.97400755667507</v>
+        <v>29.78913846153847</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3846546947585895</v>
+        <v>0.2960802581901413</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>F06</t>
+          <t>F04</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1110</v>
+        <v>423</v>
       </c>
       <c r="C42" t="n">
-        <v>62.01382612612612</v>
+        <v>61.29966113744076</v>
       </c>
       <c r="D42" t="n">
-        <v>0.4333865858917867</v>
+        <v>0.3794213121209681</v>
       </c>
       <c r="E42" t="n">
-        <v>30.01896666666667</v>
+        <v>31.96452606635071</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4007883534913337</v>
+        <v>0.3561542519980352</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>F07</t>
+          <t>F05</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>523</v>
+        <v>794</v>
       </c>
       <c r="C43" t="n">
-        <v>63.11159082217974</v>
+        <v>61.30986397984888</v>
       </c>
       <c r="D43" t="n">
-        <v>0.4697920972092659</v>
+        <v>0.4493098336189401</v>
       </c>
       <c r="E43" t="n">
-        <v>29.47491778202677</v>
+        <v>30.97400755667507</v>
       </c>
       <c r="F43" t="n">
-        <v>0.3079466209382391</v>
+        <v>0.3846546947585895</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>G04</t>
+          <t>F06</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>123</v>
+        <v>1110</v>
       </c>
       <c r="C44" t="n">
-        <v>60.94209836065575</v>
+        <v>62.01382612612612</v>
       </c>
       <c r="D44" t="n">
-        <v>0.3090221863178383</v>
+        <v>0.4333865858917867</v>
       </c>
       <c r="E44" t="n">
-        <v>31.53756097560975</v>
+        <v>30.01896666666667</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2778161832000227</v>
+        <v>0.4007883534913337</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>G05</t>
+          <t>F07</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>156</v>
+        <v>523</v>
       </c>
       <c r="C45" t="n">
-        <v>60.89048482455495</v>
+        <v>63.11159082217974</v>
       </c>
       <c r="D45" t="n">
-        <v>0.3695014212116749</v>
+        <v>0.4697920972092659</v>
       </c>
       <c r="E45" t="n">
-        <v>30.51583333333333</v>
+        <v>29.47491778202677</v>
       </c>
       <c r="F45" t="n">
-        <v>0.3645748108894012</v>
+        <v>0.3079466209382391</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>G06</t>
+          <t>F08</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>118</v>
+        <v>56</v>
       </c>
       <c r="C46" t="n">
-        <v>61.68559322033898</v>
+        <v>64.11087499999999</v>
       </c>
       <c r="D46" t="n">
-        <v>0.3105113125286638</v>
+        <v>0.3172246872993066</v>
       </c>
       <c r="E46" t="n">
-        <v>29.35421186440678</v>
+        <v>29.71842857142857</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2444737291939881</v>
+        <v>0.2593667327180112</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>G07</t>
+          <t>G04</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>277</v>
+        <v>123</v>
       </c>
       <c r="C47" t="n">
-        <v>62.52452402563864</v>
+        <v>60.94209836065575</v>
       </c>
       <c r="D47" t="n">
-        <v>0.4083313598704171</v>
+        <v>0.3090221863178383</v>
       </c>
       <c r="E47" t="n">
-        <v>29.02874007220217</v>
+        <v>31.53756097560975</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2706386102301134</v>
+        <v>0.2778161832000227</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>H04</t>
+          <t>G05</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>429</v>
+        <v>156</v>
       </c>
       <c r="C48" t="n">
-        <v>60.39269456439827</v>
+        <v>60.89048482455495</v>
       </c>
       <c r="D48" t="n">
-        <v>0.3397184779340882</v>
+        <v>0.3695014212116749</v>
       </c>
       <c r="E48" t="n">
-        <v>31.44663869463869</v>
+        <v>30.51583333333333</v>
       </c>
       <c r="F48" t="n">
-        <v>0.357686095133581</v>
+        <v>0.3645748108894012</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>H07</t>
+          <t>G06</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C49" t="n">
-        <v>63.25054312156713</v>
+        <v>61.68559322033898</v>
       </c>
       <c r="D49" t="n">
-        <v>0.3573362437409104</v>
+        <v>0.3105113125286638</v>
       </c>
       <c r="E49" t="n">
-        <v>28.85252755905512</v>
+        <v>29.35421186440678</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2759436872476647</v>
+        <v>0.2444737291939881</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>I04</t>
+          <t>G07</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>124</v>
+        <v>277</v>
       </c>
       <c r="C50" t="n">
-        <v>58.87820739873734</v>
+        <v>62.52452402563864</v>
       </c>
       <c r="D50" t="n">
-        <v>0.3844605860380795</v>
+        <v>0.4083313598704171</v>
       </c>
       <c r="E50" t="n">
-        <v>31.74933064516129</v>
+        <v>29.02874007220217</v>
       </c>
       <c r="F50" t="n">
-        <v>0.3844287282779349</v>
+        <v>0.2706386102301134</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>I15</t>
+          <t>H04</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>194</v>
+        <v>429</v>
       </c>
       <c r="C51" t="n">
-        <v>62.70368041237113</v>
+        <v>60.39269456439827</v>
       </c>
       <c r="D51" t="n">
-        <v>0.4695271924624661</v>
+        <v>0.3397184779340882</v>
       </c>
       <c r="E51" t="n">
-        <v>29.32381443298969</v>
+        <v>31.44663869463869</v>
       </c>
       <c r="F51" t="n">
-        <v>0.2470020380523166</v>
+        <v>0.357686095133581</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>I16</t>
+          <t>H07</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="C52" t="n">
-        <v>62.47536607142857</v>
+        <v>63.25054312156713</v>
       </c>
       <c r="D52" t="n">
-        <v>0.4496270278864415</v>
+        <v>0.3573362437409104</v>
       </c>
       <c r="E52" t="n">
-        <v>28.57652678571429</v>
+        <v>28.85252755905512</v>
       </c>
       <c r="F52" t="n">
-        <v>0.2834270490614266</v>
+        <v>0.2759436872476647</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>I17</t>
+          <t>I04</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="C53" t="n">
-        <v>62.50142592592593</v>
+        <v>58.87820739873734</v>
       </c>
       <c r="D53" t="n">
-        <v>0.5183150265381601</v>
+        <v>0.3844605860380795</v>
       </c>
       <c r="E53" t="n">
-        <v>27.81398148148148</v>
+        <v>31.74933064516129</v>
       </c>
       <c r="F53" t="n">
-        <v>0.2367893649655071</v>
+        <v>0.3844287282779349</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>J03</t>
+          <t>I15</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>103</v>
+        <v>194</v>
       </c>
       <c r="C54" t="n">
-        <v>59.51850012832831</v>
+        <v>62.70368041237113</v>
       </c>
       <c r="D54" t="n">
-        <v>0.3377070466848665</v>
+        <v>0.4695271924624661</v>
       </c>
       <c r="E54" t="n">
-        <v>32.48218446601942</v>
+        <v>29.32381443298969</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2570025593001959</v>
+        <v>0.2470020380523166</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>J04</t>
+          <t>I16</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>243</v>
+        <v>112</v>
       </c>
       <c r="C55" t="n">
-        <v>59.09054611987577</v>
+        <v>62.47536607142857</v>
       </c>
       <c r="D55" t="n">
-        <v>0.28645639159988</v>
+        <v>0.4496270278864415</v>
       </c>
       <c r="E55" t="n">
-        <v>32.09455967078189</v>
+        <v>28.57652678571429</v>
       </c>
       <c r="F55" t="n">
-        <v>0.2884016038834134</v>
+        <v>0.2834270490614266</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>K04</t>
+          <t>I17</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>363</v>
+        <v>54</v>
       </c>
       <c r="C56" t="n">
-        <v>59.47518115138299</v>
+        <v>62.50142592592593</v>
       </c>
       <c r="D56" t="n">
-        <v>0.3545641425935797</v>
+        <v>0.5183150265381601</v>
       </c>
       <c r="E56" t="n">
-        <v>32.46949035812672</v>
+        <v>27.81398148148148</v>
       </c>
       <c r="F56" t="n">
-        <v>0.4229822682079345</v>
+        <v>0.2367893649655071</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>K05</t>
+          <t>J03</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>612</v>
+        <v>103</v>
       </c>
       <c r="C57" t="n">
-        <v>59.66086274509804</v>
+        <v>59.51850012832831</v>
       </c>
       <c r="D57" t="n">
-        <v>0.4406589808119678</v>
+        <v>0.3377070466848665</v>
       </c>
       <c r="E57" t="n">
-        <v>31.66988725490196</v>
+        <v>32.48218446601942</v>
       </c>
       <c r="F57" t="n">
-        <v>0.4630349568612188</v>
+        <v>0.2570025593001959</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>K06</t>
+          <t>J04</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="C58" t="n">
-        <v>60.24740454545454</v>
+        <v>59.09054611987577</v>
       </c>
       <c r="D58" t="n">
-        <v>0.5485951437968812</v>
+        <v>0.28645639159988</v>
       </c>
       <c r="E58" t="n">
-        <v>30.81255909090909</v>
+        <v>32.09455967078189</v>
       </c>
       <c r="F58" t="n">
-        <v>0.2687802095648395</v>
+        <v>0.2884016038834134</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>K17</t>
+          <t>K04</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>134</v>
+        <v>363</v>
       </c>
       <c r="C59" t="n">
-        <v>64.08882835820896</v>
+        <v>59.47518115138299</v>
       </c>
       <c r="D59" t="n">
-        <v>0.3867341546333747</v>
+        <v>0.3545641425935797</v>
       </c>
       <c r="E59" t="n">
-        <v>28.25600746268656</v>
+        <v>32.46949035812672</v>
       </c>
       <c r="F59" t="n">
-        <v>0.6485739177688075</v>
+        <v>0.4229822682079345</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>L04</t>
+          <t>K05</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>144</v>
+        <v>612</v>
       </c>
       <c r="C60" t="n">
-        <v>60.01482517484515</v>
+        <v>59.66086274509804</v>
       </c>
       <c r="D60" t="n">
-        <v>0.3324021453899347</v>
+        <v>0.4406589808119678</v>
       </c>
       <c r="E60" t="n">
-        <v>33.12058333333333</v>
+        <v>31.66988725490196</v>
       </c>
       <c r="F60" t="n">
-        <v>0.2738965868311938</v>
+        <v>0.4630349568612188</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>L05</t>
+          <t>K06</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1306</v>
+        <v>220</v>
       </c>
       <c r="C61" t="n">
-        <v>60.02677565084228</v>
+        <v>60.24740454545454</v>
       </c>
       <c r="D61" t="n">
-        <v>0.3851099276902467</v>
+        <v>0.5485951437968812</v>
       </c>
       <c r="E61" t="n">
-        <v>31.98666156202143</v>
+        <v>30.81255909090909</v>
       </c>
       <c r="F61" t="n">
-        <v>0.4069004852644354</v>
+        <v>0.2687802095648395</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>L06</t>
+          <t>K17</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>785</v>
+        <v>134</v>
       </c>
       <c r="C62" t="n">
-        <v>60.96580186081455</v>
+        <v>64.08882835820896</v>
       </c>
       <c r="D62" t="n">
-        <v>0.5103449431331368</v>
+        <v>0.3867341546333747</v>
       </c>
       <c r="E62" t="n">
-        <v>31.13925987261146</v>
+        <v>28.25600746268656</v>
       </c>
       <c r="F62" t="n">
-        <v>0.3822881495436557</v>
+        <v>0.6485739177688075</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>L07</t>
+          <t>L04</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="C63" t="n">
-        <v>62.25270022052841</v>
+        <v>60.01482517484515</v>
       </c>
       <c r="D63" t="n">
-        <v>0.2944997418175912</v>
+        <v>0.3324021453899347</v>
       </c>
       <c r="E63" t="n">
-        <v>30.78747328244276</v>
+        <v>33.12058333333333</v>
       </c>
       <c r="F63" t="n">
-        <v>0.3455817493291252</v>
+        <v>0.2738965868311938</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>M04</t>
+          <t>L05</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>609</v>
+        <v>1306</v>
       </c>
       <c r="C64" t="n">
-        <v>60.50628485984618</v>
+        <v>60.02677565084228</v>
       </c>
       <c r="D64" t="n">
-        <v>0.3530344367249803</v>
+        <v>0.3851099276902467</v>
       </c>
       <c r="E64" t="n">
-        <v>33.28510344827586</v>
+        <v>31.98666156202143</v>
       </c>
       <c r="F64" t="n">
-        <v>0.3146889868237766</v>
+        <v>0.4069004852644354</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>M05</t>
+          <t>L06</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>526</v>
+        <v>785</v>
       </c>
       <c r="C65" t="n">
-        <v>60.66249113772188</v>
+        <v>60.96580186081455</v>
       </c>
       <c r="D65" t="n">
-        <v>0.3827273903545674</v>
+        <v>0.5103449431331368</v>
       </c>
       <c r="E65" t="n">
-        <v>32.3681844106464</v>
+        <v>31.13925987261146</v>
       </c>
       <c r="F65" t="n">
-        <v>0.3976223897770711</v>
+        <v>0.3822881495436557</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>M06</t>
+          <t>L07</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>752</v>
+        <v>131</v>
       </c>
       <c r="C66" t="n">
-        <v>61.52344044317348</v>
+        <v>62.25270022052841</v>
       </c>
       <c r="D66" t="n">
-        <v>0.4590215104669056</v>
+        <v>0.2944997418175912</v>
       </c>
       <c r="E66" t="n">
-        <v>31.48929122340425</v>
+        <v>30.78747328244276</v>
       </c>
       <c r="F66" t="n">
-        <v>0.3478825409005126</v>
+        <v>0.3455817493291252</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>M07</t>
+          <t>M04</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1086</v>
+        <v>609</v>
       </c>
       <c r="C67" t="n">
-        <v>62.80338950276244</v>
+        <v>60.50628485984618</v>
       </c>
       <c r="D67" t="n">
-        <v>0.7018768591793737</v>
+        <v>0.3530344367249803</v>
       </c>
       <c r="E67" t="n">
-        <v>31.01546316758748</v>
+        <v>33.28510344827586</v>
       </c>
       <c r="F67" t="n">
-        <v>0.3213689497543431</v>
+        <v>0.3146889868237766</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>M08</t>
+          <t>M05</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>891</v>
+        <v>526</v>
       </c>
       <c r="C68" t="n">
-        <v>63.53099887766555</v>
+        <v>60.66249113772188</v>
       </c>
       <c r="D68" t="n">
-        <v>0.5724599702225107</v>
+        <v>0.3827273903545674</v>
       </c>
       <c r="E68" t="n">
-        <v>30.79931088664422</v>
+        <v>32.3681844106464</v>
       </c>
       <c r="F68" t="n">
-        <v>0.3179726849550961</v>
+        <v>0.3976223897770711</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>N04</t>
+          <t>M06</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>402</v>
+        <v>752</v>
       </c>
       <c r="C69" t="n">
-        <v>61.15615479775461</v>
+        <v>61.52344044317348</v>
       </c>
       <c r="D69" t="n">
-        <v>0.3763500056684036</v>
+        <v>0.4590215104669056</v>
       </c>
       <c r="E69" t="n">
-        <v>33.60825373134328</v>
+        <v>31.48929122340425</v>
       </c>
       <c r="F69" t="n">
-        <v>0.4085970966143775</v>
+        <v>0.3478825409005126</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>N05</t>
+          <t>M07</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>594</v>
+        <v>1086</v>
       </c>
       <c r="C70" t="n">
-        <v>61.15800568916333</v>
+        <v>62.80338950276244</v>
       </c>
       <c r="D70" t="n">
-        <v>0.3446938022061293</v>
+        <v>0.7018768591793737</v>
       </c>
       <c r="E70" t="n">
-        <v>32.67709764309765</v>
+        <v>31.01546316758748</v>
       </c>
       <c r="F70" t="n">
-        <v>0.4478797230932445</v>
+        <v>0.3213689497543431</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>N06</t>
+          <t>M08</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>445</v>
+        <v>891</v>
       </c>
       <c r="C71" t="n">
-        <v>61.99652006818194</v>
+        <v>63.53099887766555</v>
       </c>
       <c r="D71" t="n">
-        <v>0.3701170700731597</v>
+        <v>0.5724599702225107</v>
       </c>
       <c r="E71" t="n">
-        <v>31.66148764044944</v>
+        <v>30.79931088664422</v>
       </c>
       <c r="F71" t="n">
-        <v>0.359933190373762</v>
+        <v>0.3179726849550961</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>N07</t>
+          <t>N03</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>737</v>
+        <v>42</v>
       </c>
       <c r="C72" t="n">
-        <v>63.28469348432676</v>
+        <v>61.51252500000008</v>
       </c>
       <c r="D72" t="n">
-        <v>0.4682108012547152</v>
+        <v>0.3109298142269343</v>
       </c>
       <c r="E72" t="n">
-        <v>31.20047489823609</v>
+        <v>33.89535714285714</v>
       </c>
       <c r="F72" t="n">
-        <v>0.3172010152967913</v>
+        <v>0.247670943508728</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>N08</t>
+          <t>N04</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2825</v>
+        <v>402</v>
       </c>
       <c r="C73" t="n">
-        <v>63.98636886425823</v>
+        <v>61.15615479775461</v>
       </c>
       <c r="D73" t="n">
-        <v>0.3875893443635896</v>
+        <v>0.3763500056684036</v>
       </c>
       <c r="E73" t="n">
-        <v>30.97673805309734</v>
+        <v>33.60825373134328</v>
       </c>
       <c r="F73" t="n">
-        <v>0.3033768876918445</v>
+        <v>0.4085970966143775</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>N09</t>
+          <t>N05</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>631</v>
+        <v>594</v>
       </c>
       <c r="C74" t="n">
-        <v>64.55852369327127</v>
+        <v>61.15800568916333</v>
       </c>
       <c r="D74" t="n">
-        <v>0.4329010366407055</v>
+        <v>0.3446938022061293</v>
       </c>
       <c r="E74" t="n">
-        <v>31.01816006339143</v>
+        <v>32.67709764309765</v>
       </c>
       <c r="F74" t="n">
-        <v>0.3323999982683625</v>
+        <v>0.4478797230932445</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>O04</t>
+          <t>N06</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
       <c r="C75" t="n">
-        <v>63.82334119955856</v>
+        <v>61.99652006818194</v>
       </c>
       <c r="D75" t="n">
-        <v>0.3435300586069744</v>
+        <v>0.3701170700731597</v>
       </c>
       <c r="E75" t="n">
-        <v>33.62073638968482</v>
+        <v>31.66148764044944</v>
       </c>
       <c r="F75" t="n">
-        <v>0.38072927588047</v>
+        <v>0.359933190373762</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>O05</t>
+          <t>N07</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>286</v>
+        <v>737</v>
       </c>
       <c r="C76" t="n">
-        <v>63.90437138450557</v>
+        <v>63.28469348432676</v>
       </c>
       <c r="D76" t="n">
-        <v>0.3424093577336183</v>
+        <v>0.4682108012547152</v>
       </c>
       <c r="E76" t="n">
-        <v>32.73797202797202</v>
+        <v>31.20047489823609</v>
       </c>
       <c r="F76" t="n">
-        <v>0.3870263528740186</v>
+        <v>0.3172010152967913</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>O06</t>
+          <t>N08</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>474</v>
+        <v>2825</v>
       </c>
       <c r="C77" t="n">
-        <v>64.8413670886076</v>
+        <v>63.98636886425823</v>
       </c>
       <c r="D77" t="n">
-        <v>0.4300940485084745</v>
+        <v>0.3875893443635896</v>
       </c>
       <c r="E77" t="n">
-        <v>31.85531012658228</v>
+        <v>30.97673805309734</v>
       </c>
       <c r="F77" t="n">
-        <v>0.328529967714487</v>
+        <v>0.3033768876918445</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>O07</t>
+          <t>N09</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>829</v>
+        <v>631</v>
       </c>
       <c r="C78" t="n">
-        <v>66.14171020748641</v>
+        <v>64.55852369327127</v>
       </c>
       <c r="D78" t="n">
-        <v>0.4566555387689955</v>
+        <v>0.4329010366407055</v>
       </c>
       <c r="E78" t="n">
-        <v>31.42784921592281</v>
+        <v>31.01816006339143</v>
       </c>
       <c r="F78" t="n">
-        <v>0.3045710843441395</v>
+        <v>0.3323999982683625</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>O08</t>
+          <t>O04</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2943</v>
+        <v>349</v>
       </c>
       <c r="C79" t="n">
-        <v>66.79819903917019</v>
+        <v>63.82334119955856</v>
       </c>
       <c r="D79" t="n">
-        <v>0.4290883517648772</v>
+        <v>0.3435300586069744</v>
       </c>
       <c r="E79" t="n">
-        <v>31.30096466190962</v>
+        <v>33.62073638968482</v>
       </c>
       <c r="F79" t="n">
-        <v>0.3176080975198945</v>
+        <v>0.38072927588047</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>O09</t>
+          <t>O05</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1292</v>
+        <v>286</v>
       </c>
       <c r="C80" t="n">
-        <v>67.24933733134485</v>
+        <v>63.90437138450557</v>
       </c>
       <c r="D80" t="n">
-        <v>0.3480107766360133</v>
+        <v>0.3424093577336183</v>
       </c>
       <c r="E80" t="n">
-        <v>31.20431269349847</v>
+        <v>32.73797202797202</v>
       </c>
       <c r="F80" t="n">
-        <v>0.321139823322653</v>
+        <v>0.3870263528740186</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>O06</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>188</v>
+        <v>474</v>
       </c>
       <c r="C81" t="n">
-        <v>64.02356914893616</v>
+        <v>64.8413670886076</v>
       </c>
       <c r="D81" t="n">
-        <v>0.3526877205080263</v>
+        <v>0.4300940485084745</v>
       </c>
       <c r="E81" t="n">
-        <v>33.57715425531915</v>
+        <v>31.85531012658228</v>
       </c>
       <c r="F81" t="n">
-        <v>0.4013017019556864</v>
+        <v>0.328529967714487</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>O07</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>613</v>
+        <v>829</v>
       </c>
       <c r="C82" t="n">
-        <v>64.0855171288744</v>
+        <v>66.14171020748641</v>
       </c>
       <c r="D82" t="n">
-        <v>0.3649359461777333</v>
+        <v>0.4566555387689955</v>
       </c>
       <c r="E82" t="n">
-        <v>32.64226427406199</v>
+        <v>31.42784921592281</v>
       </c>
       <c r="F82" t="n">
-        <v>0.4246501144692691</v>
+        <v>0.3045710843441395</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>O08</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>755</v>
+        <v>2943</v>
       </c>
       <c r="C83" t="n">
-        <v>64.71391258278146</v>
+        <v>66.79819903917019</v>
       </c>
       <c r="D83" t="n">
-        <v>0.446686970161289</v>
+        <v>0.4290883517648772</v>
       </c>
       <c r="E83" t="n">
-        <v>31.83215894039736</v>
+        <v>31.30096466190962</v>
       </c>
       <c r="F83" t="n">
-        <v>0.3794579611424352</v>
+        <v>0.3176080975198945</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>P07</t>
+          <t>O09</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>950</v>
+        <v>1292</v>
       </c>
       <c r="C84" t="n">
-        <v>65.89744105263159</v>
+        <v>67.24933733134485</v>
       </c>
       <c r="D84" t="n">
-        <v>0.4957361099776111</v>
+        <v>0.3480107766360133</v>
       </c>
       <c r="E84" t="n">
-        <v>31.28123368421052</v>
+        <v>31.20431269349847</v>
       </c>
       <c r="F84" t="n">
-        <v>0.2933016663726152</v>
+        <v>0.321139823322653</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1302</v>
+        <v>188</v>
       </c>
       <c r="C85" t="n">
-        <v>67.00384792626728</v>
+        <v>64.02356914893616</v>
       </c>
       <c r="D85" t="n">
-        <v>0.4370315977438876</v>
+        <v>0.3526877205080263</v>
       </c>
       <c r="E85" t="n">
-        <v>31.22556221198156</v>
+        <v>33.57715425531915</v>
       </c>
       <c r="F85" t="n">
-        <v>0.2898855678419216</v>
+        <v>0.4013017019556864</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>731</v>
+        <v>613</v>
       </c>
       <c r="C86" t="n">
-        <v>67.48942270861833</v>
+        <v>64.0855171288744</v>
       </c>
       <c r="D86" t="n">
-        <v>0.3267193840707144</v>
+        <v>0.3649359461777333</v>
       </c>
       <c r="E86" t="n">
-        <v>31.1718659370725</v>
+        <v>32.64226427406199</v>
       </c>
       <c r="F86" t="n">
-        <v>0.2933097368417453</v>
+        <v>0.4246501144692691</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>P18</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>46</v>
+        <v>755</v>
       </c>
       <c r="C87" t="n">
-        <v>66.20515217391306</v>
+        <v>64.71391258278146</v>
       </c>
       <c r="D87" t="n">
-        <v>0.2893129768645558</v>
+        <v>0.446686970161289</v>
       </c>
       <c r="E87" t="n">
-        <v>26.26376086956521</v>
+        <v>31.83215894039736</v>
       </c>
       <c r="F87" t="n">
-        <v>0.236004899063245</v>
+        <v>0.3794579611424352</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>Q04</t>
+          <t>P07</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>133</v>
+        <v>950</v>
       </c>
       <c r="C88" t="n">
-        <v>64.16872180451126</v>
+        <v>65.89744105263159</v>
       </c>
       <c r="D88" t="n">
-        <v>0.3574946627370337</v>
+        <v>0.4957361099776111</v>
       </c>
       <c r="E88" t="n">
-        <v>33.12652631578948</v>
+        <v>31.28123368421052</v>
       </c>
       <c r="F88" t="n">
-        <v>0.4103473877470009</v>
+        <v>0.2933016663726152</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>Q06</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>306</v>
+        <v>1302</v>
       </c>
       <c r="C89" t="n">
-        <v>64.79118300653596</v>
+        <v>67.00384792626728</v>
       </c>
       <c r="D89" t="n">
-        <v>0.4749884338173321</v>
+        <v>0.4370315977438876</v>
       </c>
       <c r="E89" t="n">
-        <v>31.37957843137255</v>
+        <v>31.22556221198156</v>
       </c>
       <c r="F89" t="n">
-        <v>0.3526571620056501</v>
+        <v>0.2898855678419216</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>R05</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>98</v>
+        <v>731</v>
       </c>
       <c r="C90" t="n">
-        <v>63.76971428571429</v>
+        <v>67.48942270861833</v>
       </c>
       <c r="D90" t="n">
-        <v>0.2889861941480306</v>
+        <v>0.3267193840707144</v>
       </c>
       <c r="E90" t="n">
-        <v>32.00479591836735</v>
+        <v>31.1718659370725</v>
       </c>
       <c r="F90" t="n">
-        <v>0.3138337971414779</v>
+        <v>0.2933097368417453</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>P18</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C91" t="n">
-        <v>66.22392105263158</v>
+        <v>66.20515217391306</v>
       </c>
       <c r="D91" t="n">
-        <v>0.4394732122594388</v>
+        <v>0.2893129768645558</v>
       </c>
       <c r="E91" t="n">
-        <v>28.85063157894736</v>
+        <v>26.26376086956521</v>
       </c>
       <c r="F91" t="n">
-        <v>0.1969754755042832</v>
+        <v>0.236004899063245</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>T04</t>
+          <t>Q04</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="C92" t="n">
-        <v>62.1407927927928</v>
+        <v>64.16872180451126</v>
       </c>
       <c r="D92" t="n">
-        <v>0.4346443014430135</v>
+        <v>0.3574946627370337</v>
       </c>
       <c r="E92" t="n">
-        <v>31.53715315315316</v>
+        <v>33.12652631578948</v>
       </c>
       <c r="F92" t="n">
-        <v>0.3860541599075828</v>
+        <v>0.4103473877470009</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>T17</t>
+          <t>Q06</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>44</v>
+        <v>306</v>
       </c>
       <c r="C93" t="n">
-        <v>64.97688636363638</v>
+        <v>64.79118300653596</v>
       </c>
       <c r="D93" t="n">
-        <v>0.3337856699296916</v>
+        <v>0.4749884338173321</v>
       </c>
       <c r="E93" t="n">
-        <v>27.46806818181818</v>
+        <v>31.37957843137255</v>
       </c>
       <c r="F93" t="n">
-        <v>0.2607513093950628</v>
+        <v>0.3526571620056501</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>R05</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="C94" t="n">
-        <v>59.18932786885245</v>
+        <v>63.76971428571429</v>
       </c>
       <c r="D94" t="n">
-        <v>0.29817352310201</v>
+        <v>0.2889861941480306</v>
       </c>
       <c r="E94" t="n">
-        <v>31.4945737704918</v>
+        <v>32.00479591836735</v>
       </c>
       <c r="F94" t="n">
-        <v>0.239599047523791</v>
+        <v>0.3138337971414779</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>V04</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>165</v>
+        <v>38</v>
       </c>
       <c r="C95" t="n">
-        <v>58.91941818181817</v>
+        <v>66.22392105263158</v>
       </c>
       <c r="D95" t="n">
-        <v>0.357436200244434</v>
+        <v>0.4394732122594388</v>
       </c>
       <c r="E95" t="n">
-        <v>32.58913333333334</v>
+        <v>28.85063157894736</v>
       </c>
       <c r="F95" t="n">
-        <v>0.373738054976174</v>
+        <v>0.1969754755042832</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>X03</t>
+          <t>T04</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>172</v>
+        <v>111</v>
       </c>
       <c r="C96" t="n">
-        <v>59.49155232558137</v>
+        <v>62.1407927927928</v>
       </c>
       <c r="D96" t="n">
-        <v>0.3166361212946892</v>
+        <v>0.4346443014430135</v>
       </c>
       <c r="E96" t="n">
-        <v>34.63825000000001</v>
+        <v>31.53715315315316</v>
       </c>
       <c r="F96" t="n">
-        <v>0.2502281081426526</v>
+        <v>0.3860541599075828</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
+          <t>T17</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>44</v>
+      </c>
+      <c r="C97" t="n">
+        <v>64.97688636363638</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0.3337856699296916</v>
+      </c>
+      <c r="E97" t="n">
+        <v>27.46806818181818</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.2607513093950628</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>U05</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>61</v>
+      </c>
+      <c r="C98" t="n">
+        <v>59.18932786885245</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0.29817352310201</v>
+      </c>
+      <c r="E98" t="n">
+        <v>31.4945737704918</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.239599047523791</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>V04</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>165</v>
+      </c>
+      <c r="C99" t="n">
+        <v>58.91941818181817</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0.357436200244434</v>
+      </c>
+      <c r="E99" t="n">
+        <v>32.58913333333334</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0.373738054976174</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>X03</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>172</v>
+      </c>
+      <c r="C100" t="n">
+        <v>59.49155232558137</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0.3166361212946892</v>
+      </c>
+      <c r="E100" t="n">
+        <v>34.63825000000001</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.2502281081426526</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>X04</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>72</v>
+      </c>
+      <c r="C101" t="n">
+        <v>59.0404027777778</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0.2962335161716088</v>
+      </c>
+      <c r="E101" t="n">
+        <v>34.15380555555555</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.2571836589163094</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
           <t>X05</t>
         </is>
       </c>
-      <c r="B97" t="n">
+      <c r="B102" t="n">
         <v>206</v>
       </c>
-      <c r="C97" t="n">
+      <c r="C102" t="n">
         <v>59.11328155339806</v>
       </c>
-      <c r="D97" t="n">
+      <c r="D102" t="n">
         <v>0.3227215703819935</v>
       </c>
-      <c r="E97" t="n">
+      <c r="E102" t="n">
         <v>33.33864563106797</v>
       </c>
-      <c r="F97" t="n">
+      <c r="F102" t="n">
         <v>0.3226322046405221</v>
       </c>
     </row>
